--- a/old/260830.xlsx
+++ b/old/260830.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763FFCF-6BBB-4D05-B65A-2AA4477C1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D95D752-BA6A-4D5E-9F0C-26249E114CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7910" yWindow="2720" windowWidth="15010" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="3700" windowWidth="15010" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,12 +28,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>zugewiesen</t>
-  </si>
-  <si>
-    <t>Gestrigen</t>
-  </si>
-  <si>
     <t>ehrenamtliches Engagement</t>
   </si>
   <si>
@@ -53,6 +47,14 @@
   </si>
   <si>
     <t>Justizminister</t>
+  </si>
+  <si>
+    <t>Gestrigen昨天的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zugewiesen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -388,17 +390,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -417,27 +419,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
